--- a/ThemePark_Engineers_Grade5_Python_Camp_MASTER.xlsx
+++ b/ThemePark_Engineers_Grade5_Python_Camp_MASTER.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="405">
   <si>
     <t xml:space="preserve">Theme Park Engineers - Grade 5 Python Camp</t>
   </si>
@@ -108,16 +108,16 @@
     <t xml:space="preserve">Dictionaries, classes, file I/O, and exception handling are out of scope entirely.</t>
   </si>
   <si>
-    <t xml:space="preserve">One machine-learning block is included because the 2026 standards require it at grade 5. It uses a no-code training tool; it is not a Python block.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pygame is the one third-party package (pip install pygame). It draws the Day-4 coaster at 60 frames a second; on managed machines the install can need an IT ticket, so verify it on real camp hardware by Tuesday. The turtle edition of the coaster needs no install and is the full fallback.</t>
+    <t xml:space="preserve">No machine-learning block: earlier drafts included one, but it was removed when the coaster became the capstone; the camp claims no ALG-ML standards. The Standards Alignment tab lists everything the camp deliberately does not cover.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pygame is the one third-party package (pip install pygame). It draws the Day-3 coaster at 60 frames a second; on managed machines the install can need an IT ticket, so verify it on real camp hardware by Tuesday. The turtle edition of the coaster needs no install and is the full fallback.</t>
   </si>
   <si>
     <t xml:space="preserve">PACING CAUTION FOR THE CAMP FORMAT</t>
   </si>
   <si>
-    <t xml:space="preserve">Compression trades spaced practice for momentum. A weekly course gets fifteen nights of sleep between iteration and functions; this camp gets two. Expect Day 4 (functions) to feel earlier than it 'should.' The 15-minute Park Briefing each day is not a warm-up filler - it is the replacement for spaced retrieval, and every briefing re-traces the previous day's build. Do not cut it to buy build time.</t>
+    <t xml:space="preserve">Compression trades spaced practice for momentum. A weekly course gets fifteen nights of sleep between iteration and functions; this camp gets two. Expect Day 3 (functions) to feel earlier than it 'should.' The 15-minute Park Briefing each day is not a warm-up filler - it is the replacement for spaced retrieval, and every briefing re-traces the previous day's build. Do not cut it to buy build time.</t>
   </si>
   <si>
     <t xml:space="preserve">Three hours is long for ten-year-olds. The schedule assumes a real 15-minute break and a change of activity mode roughly every 25-30 minutes within blocks (unplugged, typed, shared). Friday is the tightest day; the pressure valve is the nested-loop exploration on Tuesday, which can be shortened to bank 15 minutes of capstone planning into Thursday's close.</t>
@@ -204,112 +204,112 @@
     <t xml:space="preserve">Believing the computer infers intent. Reading = as 'equals' rather than 'gets'. Believing the loop body runs once. Using the interior angle instead of 360/sides.</t>
   </si>
   <si>
-    <t xml:space="preserve">Safety Gates &amp; the Midway - Selection &amp; Lists</t>
+    <t xml:space="preserve">Safety Gates &amp; the Midway - Selection, Lists &amp; the Toolbox</t>
   </si>
   <si>
     <t xml:space="preserve">Tuesday 1:00-4:00</t>
   </si>
   <si>
-    <t xml:space="preserve">How does a program make a decision, and how does it hold many values at once?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Write conditions using comparison operators; branch with if / elif / else; explain why only one branch executes; combine a loop with a conditional; create a list and access an element by index; explain zero-based indexing; iterate over a list with a for loop.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if / elif / else, ==, &lt;, &gt;, booleans, lists, indexing, len()</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ride safety gate (height check) + midway guessing game with hot/cold hints + printed ride roster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALG-PS-01; PRO-PD; PRO-VD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sort 'tall enough to ride?' scenario cards into True/False before coding. Index hunt on the ride queue. Class Card 01: the coaster track-list preview.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confusing = with ==. Lists start at 1 - label the first queue spot 0 and let the discomfort sit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Prize Wheel &amp; Blueprint Stamps - Randomness &amp; Functions</t>
+    <t xml:space="preserve">How does a program decide, remember, surprise - and stamp?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write conditions using comparison operators; branch with if / elif / else; explain why only one branch executes; create a list and pick items out by index; select a random element with random.choice(); define a function with def, call it by name, and pass a parameter to change its behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if / elif / else, ==, &lt;, &gt;, booleans, lists, indexing, len(), random.choice(), def, parameters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ride safety gate + printed park map + prize-wheel spin + draw_wheel(spokes) blueprint stamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALG-PS-01; PRO-PD; PRO-VD; PRO-RD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sort 'tall enough to ride?' scenario cards into True/False before coding. Index hunt on the ride roster. Run the defined-but-never-called function and sit with the silence. Test Ride: Class Cards 01-03 - the track-list preview, the sqrt ladder, and the no-wheels ramp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confusing = with ==. Lists start at 1 - label the first queue spot 0 and let the discomfort sit. Defining is calling - the silent run is the diagnosis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Coaster Build - Capstone</t>
   </si>
   <si>
     <t xml:space="preserve">Wednesday 1:00-4:00</t>
   </si>
   <si>
-    <t xml:space="preserve">How do I add surprise, and how do I name a thing I do over and over?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Select a random element with random.choice(); define a function with def and call it by name; pass a parameter to change its behavior; refactor copied drawing code into draw_wheel(spokes, size).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">random.choice(), def, parameters, function calls</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prize-wheel booth program + refactored draw_wheel() blueprint stamp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRO-RD; PRO-VD; ALG-PS-01; PRO-PD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Give students working code and ask which lines repeat. Run the defined-but-never-called function and sit with the silence. Class Card 02: the sqrt ladder + Fury 325 check. Class Card 03: the no-wheels text ramp (the position line and the missing-shove silence).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Defining is calling - show the silent no-output run and let them diagnose it. A list is a single value - the list is the shelf, the index picks the ride.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Coaster Build - Capstone</t>
+    <t xml:space="preserve">Can I plan, build, and soft-launch a ride of my own - and where does a roller coaster's speed come from?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trace a live simulation against a track list using the on-screen dashboard; design a coaster track that completes (first hill tallest, ends at 0) and revise it with a goal; build an Operator's Booth with sequence, a loop, and a decision that selects the track; narrate the three physics lines at a one-partner soft launch; read a traceback and debug independently during the build.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None new - the pygame coaster engine is provided read-only (math.sqrt, the track list, and the position line all previewed on Day 2); student-selected review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operator's Booth + student-designed coaster track (Version 1 -&gt; Version 2), soft-launched for one guest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALG-PS-01; PRO-PD; PRO-VD; PRO-RD; PRO-TR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blueprint approved before any code - a new track list alone is not a capstone. Ride Log Grid A checked live against the dashboard. Soft-launch diagnosis on the Maintenance slip.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Believing a new track list alone is a capstone - the booth is the program, the coaster is the finale. Scope creep - cap it: one screen, one loop, one decision.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expansion Day - Fix, Upgrade, Prove</t>
   </si>
   <si>
     <t xml:space="preserve">Thursday 1:00-4:00</t>
   </si>
   <si>
-    <t xml:space="preserve">Can I plan, build, and soft-launch a ride of my own - and where does a roller coaster's speed come from?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trace a live simulation against a track list using the on-screen dashboard; design a coaster track that completes (first hill tallest, ends at 0) and revise it with a goal; build an Operator's Booth with sequence, a loop, and a decision that selects the track; narrate the three physics lines at a one-partner soft launch; read a traceback and debug independently during the build.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None new - the pygame coaster engine is provided read-only (math.sqrt and the track list previewed on Days 2-3); student-selected review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operator's Booth + student-designed coaster track (Version 1 -&gt; Version 2), soft-launched for one guest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALG-PS-01; PRO-PD; PRO-VD; PRO-RD; PRO-TR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blueprint approved before any code - a new track list alone is not a capstone. Ride Log Grid A checked live against the dashboard. Soft-launch diagnosis on the Maintenance slip.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Believing a new track list alone is a capstone - the booth is the program, the coaster is the finale. Scope creep - cap it: one screen, one loop, one decision.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grand Opening - Fix, Polish, Present</t>
+    <t xml:space="preserve">Can I repair my own build - and make it better than it was?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independently diagnose and fix errors in their own program by reading the error first; ship one tested upgrade with a what-changed-and-why note; verify their own track against the live dashboard on Ride Log Grid B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None new - repair and refinement; stretch: a friction term in the drop line, a random.choice mystery track</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The repaired ride + one shipped upgrade (Version 3) + completed Ride Log Grid B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRO-TR; PRO-PD; PRO-VD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debugging log collected at the clinic. Grid B checked against the camper's own list. Upgrade note names the change and the goal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Believing stuck means failure - Thursday-morning stuck is why Expansion Day exists. Fixing without reading the error.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand Opening - Inspect, Rehearse, Present</t>
   </si>
   <si>
     <t xml:space="preserve">Friday 1:00-4:00</t>
   </si>
   <si>
-    <t xml:space="preserve">Can I repair my own build - and open it to the public?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Independently diagnose and fix errors in their own program by reading the error first; ship one tested upgrade or polish pass; present a live walkthrough narrating the three physics lines; name a human-centered design choice and who it serves or excludes; discuss who can see, change, or reach a program (the CIA triad).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None new - review and repair; stretch: a friction term in the drop line, a random.choice mystery track</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The repaired, polished attraction + Grand Opening walkthrough + reflection slip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRO-TR; PRO-PD; PRO-RD; ALG-IM-03; SYS-SE-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debugging log collected at the clinic; reflection slip collected at the walkthrough.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Believing stuck means failure - Friday-morning stuck is the plan working. Fixing without reading the error.</t>
+    <t xml:space="preserve">Can I present my ride, narrate its physics, and name who it's for?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run a final opening-day inspection; present a live walkthrough narrating the three physics lines on their own track; articulate one human-centered design choice and who it serves or excludes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None new - inspection and presentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The finished attraction + Grand Opening walkthrough + reflection slip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRO-RD; ALG-IM-03; SYS-SE-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opening-day inspection checklist passed; reflection slip collected at the walkthrough.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Believing the presentation is about perfection - it's about narration: can you say what each line does, and what you'd fix next?</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL</t>
@@ -444,10 +444,13 @@
     <t xml:space="preserve">Paper slips</t>
   </si>
   <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Re-trace + card sort</t>
   </si>
   <si>
-    <t xml:space="preserve">Re-trace Monday: one volunteer narrates the square-track loop pass by pass. Then sort 'tall enough to ride?' scenario cards into True and False piles.</t>
+    <t xml:space="preserve">Re-trace Monday: one volunteer narrates the square-track loop pass by pass. Then sort 'tall enough to ride?' scenario cards into True/False.</t>
   </si>
   <si>
     <t xml:space="preserve">Read each condition aloud as a question: 'is height over 48?'</t>
@@ -456,244 +459,253 @@
     <t xml:space="preserve">Scenario cards</t>
   </si>
   <si>
-    <t xml:space="preserve">if / elif / else</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build the Ride Safety Gate: if/else on a height check ('you must be 48 inches to ride The Comet'), then add elif for a three-way band: child rides, family rides, thrill rides. Say == aloud as 'is it the same as?'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Why did only one branch print?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Height-check starter file; == vs = color-coded card</t>
+    <t xml:space="preserve">if / elif / else + the prize wheel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build the Ride Safety Gate: if/else on a height check, then elif for three bands. Then the Prize Wheel: random.choice() on a camper-written prize list - chance vs index, two hands reaching for the same shelf.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why did only one branch print? What does random.choice() hand back - the item or its number?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Height-check starter file; == vs = color-coded card; random module cheat sheet</t>
   </si>
   <si>
     <t xml:space="preserve">Movement break.</t>
   </si>
   <si>
-    <t xml:space="preserve">Loop + conditional, then lists</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build the Midway guessing game with hot/cold hints inside a counted loop - play a classmate's booth. Then lists: numbered cups as the ride queue, first spot labeled 0. Close with the coaster preview (Class Card 01): the track list - len(track), track[0], track[7], and last index = len() minus one.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Where does the condition live relative to the loop? Why does the last index equal len() minus one?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Game starter file; numbered cups or cards; Class Card 01 printed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play the midway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campers rotate and play two classmates' guessing-game booths (two, not four - Block B runs long with the coaster preview). Index hunt on the roster: teacher points at a ride, campers name its index.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name one bug you fixed today.</t>
+    <t xml:space="preserve">Lists, then def &amp; parameters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build the ride roster and print the park map by looping the shelf. Then def: wrap the copied triangle-support block into draw_support(), run it, sit with the silence, then call it twice. Finish with draw_wheel(spokes) - one stamp, any wheel. Short build: roster + map + gate + one lucky spin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why does the last index beat len()? What broke when we forgot to call it?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class Card 01 printed; refactor worksheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomorrow's engine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two whole-class experiments from Class Cards 02-03: the sqrt ladder (44 / 63 / 89 / 99 mph vs Fury 325's real 95) and the no-wheels ramp - fourteen growing steps with nothing saying 'speed up', then delete the shove and sit with fourteen zeros.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What makes each step bigger than the last? What did deleting the shove do?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class Cards 02-03 printed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write the condition for 'height is over 48'. What are the two steps to using a stamp?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reteach flags: = where == belongs; 'defining is calling' answers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-trace + first ride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-trace Tuesday: what does the sqrt line print for drop = 80? Frame the day: today the park gets its headliner. Projector run of the finished coaster once, no code shown yet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Predict the top speed before the projector run.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projector; coaster.py tested on the teacher machine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The engine &amp; the Ride Log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assemble the engine in five staged runs from the Day 3 page: Stage 1 rails from the list (change a number, zero drawing edits); Stage 2 place the train (position 70 - HEIGHT 27, Tuesday's card live); Stage 3 first motion - it fails on purpose, parked at SPEED 0 (Tuesday's ramp silence on a real screen; diagnose before revealing); Stage 4 the chain's shove - the full ride, 19 seconds, 70 mph; Stage 5 the inspector completes the engine. Then the hinge: commit to the 55-meter answer, then run that track in your own engine and watch it come true. Ride Log Grid A: towers 3, 9, 13 minimum.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid A collected (three towers minimum). Hinge answered and run before design.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Printed Ride Logs; pygame verified on camp hardware by Tuesday, or run the week on the turtle edition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2:10-2:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short break.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2:20-2:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build Block B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capstone blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design the Operator's Booth: a visual blueprint with sequence, one loop, one decision that chooses the track, and named variables. Approval gate: a new track list alone is not a capstone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blueprint approved and signed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blueprint template; Track Design Card on the Coaster Lab page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2:45-3:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build Block B2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capstone build &amp; debug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build the booth above the engine; delete the engine's own track line - the booth chooses now. Design a track that completes (first hill tallest, ends at 0). Working Version 1 into a comment before any Version 2 experiment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V1/V2 note on the Ride Log. Debugging log begun (collected Thursday).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debug protocol poster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:30-3:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOFT LAUNCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One-partner safety inspection: run the booth live with the partner as guest; narrate the three physics lines on your own track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maintenance slip: what needs fixing tomorrow morning?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inspection pairing list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:55-4:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One line: the first thing you will fix tomorrow, and the first line you will read to fix it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Triage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run yesterday's build exactly as you left it. Three lanes on the board: RUNNING / RUNS-BUT-WRONG / STUCK. Being in STUCK this morning is why Expansion Day exists - the ribbon isn't until Friday.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every name in a lane.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Triage board; lane cards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix-It Clinic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pair debugging: one drives, the partner reads the traceback aloud, last line first. Nobody touches a keyboard that is not theirs. Teacher floats to STUCK first.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debugging log collected at the end of the block.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debug protocol poster; the week's traceback reference cards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2:25-3:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stretch Garage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every camper picks one upgrade: friction in the drop line (tune 0.01 toward 0.08 to make a 99 m build land on Fury 325s real 95 mph), the random.choice mystery track, a second booth decision, or a track redesign with a goal (Version 3). Working version into a comment first.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade chosen and started; working copy protected in a comment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coaster Lab page open for the stretch numbers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:00-3:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid B + the upgrade note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ride Log Grid B on the camper's own track: five towers circled, heights pre-filled from their list, TIME and SPEED caught live. Then the upgrade note: what changed and why - 'Raised the third hill to 40 so the middle stops dragging.'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid B matches the list at five towers. Note names the change and the goal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ride Logs (Grid B side)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgrade showcase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quick rotation: each camper shows one shipped upgrade and the Grid B row that proves their ride does what they say it does.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid B and the upgrade note collected.</t>
   </si>
   <si>
     <t xml:space="preserve">Rotation timer</t>
   </si>
   <si>
-    <t xml:space="preserve">Write the condition for 'height is over 48'. For a 4-ride roster, what is the last index?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reteach flag: = written where == belongs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Re-trace + prize draw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Re-trace Tuesday: trace the safety gate with one specific height. Then draw a prize from a hat: why is it different each time?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Predict-the-output warm-up on two snippets.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hat + prize slips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">random.choice() + the speed of falling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build the Prize Wheel booth: random.choice() on a camper-written prize list. Run it five times - why different each run? Then Class Card 02, whole-class: the speed of falling - the math.sqrt ladder (drop 20 / 40 / 80) and the Fury 325 reality check (99 m predicts 99 mph; the real ride tops at 95 - name where the missing 4 mph go).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What does random.choice() return? What did drop = 40 print?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">random module cheat sheet; Class Card 02 printed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Functions &amp; parameters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Show a program with the same six drawing lines pasted three times. Wrap the block in def draw_support() - the blueprint stamp. Run it with no call; sit with the silence. Then parameters: draw_wheel(spokes), then draw_wheel(spokes, size). Close by projecting the coaster's three dashboard lines: f-strings with speed and height flowing in - Monday's receipt, Thursday's instruments.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What broke when we forgot to call it? Compare line counts before and after.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Refactor worksheet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One stamp, three wheels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each camper shows one function producing three different wheels. Close with 15 minutes of capstone preview (Class Card 03): the engine with no wheels - run the 14-step text ramp, watch each step grow with nothing saying 'speed up', then delete the two shove lines and sit with the fourteen silent zeros. Sketch a first track shape and one booth idea on the idea slip.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What makes each step bigger than the last? What did deleting the shove do?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Idea slips; Class Card 03 printed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What are the two steps to using a function?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reteach flag: 'defining is calling' answers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Re-trace + first ride</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Re-trace Wednesday: what does the sqrt line print for drop = 80? Frame the day: today you design a ride and build it; tomorrow the park opens. Run the stock coaster once on the projector - 19 seconds, 70 mph.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Predict the top speed before the projector run.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projector; coaster.py tested on the teacher machine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The engine &amp; the Ride Log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assemble the engine in five staged runs from the Day 4 page: Stage 1 rails from the list (change a number, zero drawing edits); Stage 2 place the train (position 70 - HEIGHT 27, Tuesday's card live); Stage 3 first motion - it fails on purpose, parked at SPEED 0 (yesterday's ramp silence on a real screen; diagnose before revealing); Stage 4 the chain's shove - the full ride, 19 seconds, 70 mph; Stage 5 the inspector completes the engine. Then the hinge: commit to the 55-meter answer, then run that track in your own engine and watch it come true. Ride Log Grid A: towers 3, 9, 13 minimum, all five if time.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid A collected (three towers minimum). Hinge answered and run before design.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Printed Ride Logs; pygame verified on camp hardware by Tuesday, or run the week on the turtle edition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2:10-2:20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Short break.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2:20-2:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build Block B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capstone blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design the Operator's Booth: a visual blueprint with sequence, one loop, and the decision that chooses the track - plus the track design (10+ towers, first tallest, ends at 0, completes). Studio rule, said aloud at approval: a new track list alone is not a capstone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blueprint approved and signed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blueprint template; Track Design Card on the Coaster Lab page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2:45-3:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build Block B2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capstone build &amp; debug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build the booth above the engine; delete the engine's own track line - the booth decides. Track Version 1 -&gt; Version 2 with the what-changed note. Debugging protocol on the wall: read the error first, last line first. Teacher circulates; no fixing on the camper's behalf.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V1/V2 note on the Ride Log. Debugging log begun (collected Friday).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debug protocol poster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:30-3:55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOFT LAUNCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One-partner safety inspection: run the booth live with the partner as guest, invite them to break it (an unexpected mood answer), rehearse narrating the three physics lines, and log everything that broke or wobbled. Nothing must be perfect today; everything must be diagnosed today.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maintenance slip: what needs fixing tomorrow morning?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inspection pairing list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:55-4:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One line: the first thing you will fix tomorrow, and the first line you will read to fix it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Triage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Run yesterday's build exactly as you left it. Three lanes on the board: RUNNING (to the Stretch Garage), ALMOST (silent bugs), STUCK (traceback). Being stuck Friday morning is the plan working - the ribbon is at 3:25, not 9:00.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every name in a lane.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Triage board; lane cards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fix-It Clinic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pair debugging: one drives, the partner reads the traceback aloud, last line first. Nobody's hands on anyone else's keyboard, including the teacher's. The three likely suspects from the soft launches: a missing colon, = where == belongs, and a later hill out-talling the lift (a physics bug, not a Python bug). Every fix goes in the two-line log.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debugging log collected at the end of the block.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debug protocol poster; the week's traceback reference cards</t>
+    <t xml:space="preserve">One line: what will you polish for Friday, and which of the three opening-day checks worries you most?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opening-day inspection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run the final version once, exactly as it will run at 3:25. Three checks: completes (no banner), survives a strange answer, and you can say the three physics lines without looking.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checklist marked; anyone failing a check goes to the clinic corner.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inspection checklist on the board</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polish + clinic corner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final polish: booth wording, boarding-pass printout, park signage. The clinic corner stays open with the teacher for anyone whose inspection failed - the clinic never really closes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every ride passes all three checks by 2:10.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinic corner table; polish checklist</t>
   </si>
   <si>
     <t xml:space="preserve">Short break (Friday protects showcase time).</t>
   </si>
   <si>
-    <t xml:space="preserve">2:20-3:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stretch Garage &amp; polish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUNNING lane picks one upgrade - friction (tune 0.01 toward 0.08 to match Fury 325's 95 mph), a random.choice mystery ride, a fast-pass second decision, or boarding-pass polish. Rule: copy the working version into a comment before touching anything. ALMOST and STUCK lanes keep the clinic going.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgrade named and explained, or bug count going down.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coaster Lab page open for the stretch numbers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:00-3:25</t>
+    <t xml:space="preserve">2:20-3:25</t>
   </si>
   <si>
     <t xml:space="preserve">Rehearsal</t>
   </si>
   <si>
-    <t xml:space="preserve">Two-minute run-through with a partner as guest: narrate the three physics lines on your own track, and answer 'why does it speed up at the bottom?' without saying 'the code tells it to.' Draft the reflection slip: one design choice, who the ride serves - and who it doesn't.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reflection slip drafted.</t>
+    <t xml:space="preserve">Two-minute run-through with a partner as guest: narrate the three physics lines, name the design choice and its audience, take one question. Swap. Reflection slip drafted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reflection slip drafted; narration heard once by a partner.</t>
   </si>
   <si>
     <t xml:space="preserve">Presentation order posted; timer</t>
@@ -705,7 +717,7 @@
     <t xml:space="preserve">GRAND OPENING</t>
   </si>
   <si>
-    <t xml:space="preserve">Two-minute walkthroughs for the room: live run with a classmate as guest, the three-lines narration, one design choice and its audience. Close with the security conversation anchored to their own program: who can see, change, or reach it? Reflection slips collected.</t>
+    <t xml:space="preserve">Two-minute walkthroughs for the room: live run with a classmate as guest, the three-line narration, the design choice and who it serves or excludes, and the security close: who can see, change, or reach your program?</t>
   </si>
   <si>
     <t xml:space="preserve">Reflection slip collected. Each camper narrates the three lines.</t>
@@ -714,7 +726,7 @@
     <t xml:space="preserve">Presentation timer; families invited if the site allows</t>
   </si>
   <si>
-    <t xml:space="preserve">Of everything you fixed this week, which fix taught you the most - and why?</t>
+    <t xml:space="preserve">Of everything you fixed this week, which fix taught you the most - and what would Version 4 be?</t>
   </si>
   <si>
     <t xml:space="preserve">CSTA 2026 Grade-5 Alignment - Theme Park Engineers camp</t>
@@ -759,61 +771,58 @@
     <t xml:space="preserve">Create a visual representation of an algorithm that includes variables and a combination of sequence, events, iteration, and selection to solve a problem or express an idea.</t>
   </si>
   <si>
+    <t xml:space="preserve">1, 2, 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approved capstone blueprint (Day 3) showing sequence, a loop, and the track-choosing decision with its variables - plus the built program that follows it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E5-ALG-IM-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impacts of Algorithms &amp; Design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Articulate how human-centered design principles are incorporated into the development of a computing technology.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand Opening reflection slip: one design choice in the camper's own ride and who it serves or excludes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E5-SYS-SE-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems &amp; Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Describe the concepts of the CIA triad and how each component is important in protecting information.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand Opening debrief: who can see, change, or reach your program.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E5-PRO-PD-??</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs verification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program Development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grade-5 progression: students refine programs through feedback, compare solutions, and modify existing code to create new programs. [Confirm exact code and wording at source.]</t>
+  </si>
+  <si>
     <t xml:space="preserve">1, 2, 3, 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Approved capstone blueprint (Day 4) showing sequence, a loop, and the track-choosing branch - plus the built booth that follows it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E5-ALG-IM-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Impacts of Algorithms &amp; Design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Articulate how human-centered design principles are incorporated into the development of a computing technology.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grand Opening reflection slip: one design choice in the camper's own ride and who it serves or excludes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E5-SYS-SE-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems &amp; Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Describe the concepts of the CIA triad and how each component is important in protecting information.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grand Opening debrief: who can see, change, or reach your program.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E5-PRO-PD-??</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs verification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Program Development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grade-5 progression: students refine programs through feedback, compare solutions, and modify existing code to create new programs. [Confirm exact code and wording at source.]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1, 2, 3, 4, 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working park artifact each day; Day-3 refactor of the copied supports into draw_wheel(spokes, size); Day-4 track Version 1 -&gt; Version 2 with the what-changed note; Day-5 fix-and-upgrade cycle.</t>
+    <t xml:space="preserve">Working park artifact each day; Day-2 refactor of the copied supports into draw_wheel; the Day-4 upgrade note (what changed and why).</t>
   </si>
   <si>
     <t xml:space="preserve">E5-PRO-VD-??</t>
@@ -825,7 +834,7 @@
     <t xml:space="preserve">Grade-5 progression: students identify and label data in everyday contexts, recognize values that change over time, and identify and trace data in programs. [Confirm exact code and wording at source.]</t>
   </si>
   <si>
-    <t xml:space="preserve">Completed ticket-price trace table; correct index identification on the ride roster; Day-4 Ride Log Grid A checked against the live dashboard.</t>
+    <t xml:space="preserve">Completed ticket-price trace table; correct index identification on the ride roster; Ride Log Grid A on the stock track (Day 3) and Grid B on the camper's own track (Day 4).</t>
   </si>
   <si>
     <t xml:space="preserve">E5-PRO-RD-??</t>
@@ -837,10 +846,10 @@
     <t xml:space="preserve">Grade-5 progression: students describe how code completes tasks and explain program steps. [Confirm exact code and wording at source.]</t>
   </si>
   <si>
-    <t xml:space="preserve">3, 4, 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Predict-the-output warm-ups; Grand Opening narration of the three physics lines.</t>
+    <t xml:space="preserve">2, 3, 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Predict-the-output warm-ups; the sqrt ladder and the no-wheels ramp (Day 2); Grand Opening narration of the three physics lines.</t>
   </si>
   <si>
     <t xml:space="preserve">E5-PRO-TR-??</t>
@@ -852,10 +861,10 @@
     <t xml:space="preserve">Grade-5 progression: students identify and debug errors in simple programs. [Confirm exact code and wording at source.]</t>
   </si>
   <si>
-    <t xml:space="preserve">1, 4, 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Independent two-line debugging log, Day-4 build through Day-5 fix-it clinic (collected Friday).</t>
+    <t xml:space="preserve">1, 3, 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independent two-line debugging log, Day-3 build through Day-4 Expansion clinic (collected Day 4).</t>
   </si>
   <si>
     <t xml:space="preserve">Note</t>
@@ -1098,7 +1107,7 @@
     <t xml:space="preserve">Stuck means failure</t>
   </si>
   <si>
-    <t xml:space="preserve">Camper freezes at Friday triage, embarrassed the build is broken.</t>
+    <t xml:space="preserve">Camper freezes at Thursday triage, embarrassed the build is broken.</t>
   </si>
   <si>
     <t xml:space="preserve">School often grades the artifact, not the repair.</t>
@@ -1108,6 +1117,15 @@
   </si>
   <si>
     <t xml:space="preserve">Being stuck Friday morning is the plan working. The rubric's protected row is the repair, not the shine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The presentation is about perfection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camper freezes at the microphone when one run hiccups.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">School often rewards flawless performance; the walkthrough rewards narration and repair.</t>
   </si>
   <si>
     <t xml:space="preserve">Assessment - Theme Park Engineers camp</t>
@@ -2434,600 +2452,600 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="17" t="s">
+      <c r="A9" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E9" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="E10" s="12" t="s">
+      <c r="D10" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="E10" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="F10" s="1" t="s">
         <v>146</v>
       </c>
+      <c r="G10" s="1" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="19" t="s">
+      <c r="A11" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E11" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="F11" s="19" t="s">
+      <c r="E11" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="1" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" s="12" t="s">
+      <c r="A12" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="E12" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="C13" s="12" t="s">
+      <c r="F24" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="C14" s="12" t="s">
+      <c r="D27" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D28" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E14" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="G14" s="12" t="s">
+      <c r="E28" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" s="17" t="s">
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C29" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D15" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="G15" s="17" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="B16" s="12" t="s">
+      <c r="D29" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C30" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D16" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="C17" s="19" t="s">
+      <c r="D30" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D31" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E17" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="F17" s="19" t="s">
+      <c r="E31" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="G31" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="C18" s="12" t="s">
+    <row r="32" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D18" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="C19" s="12" t="s">
+      <c r="D32" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D19" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="G19" s="12" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="C20" s="12" t="s">
+      <c r="D33" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D34" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E20" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>176</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="G22" s="12" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D23" s="19" t="s">
+      <c r="E34" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E23" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="G26" s="12" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="G27" s="12" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="C28" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>206</v>
-      </c>
-      <c r="F28" s="17" t="s">
-        <v>207</v>
-      </c>
-      <c r="G28" s="17" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="G29" s="12" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="G30" s="19" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="F32" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="G32" s="12" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="G34" s="12" t="s">
+      <c r="G34" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -3061,230 +3079,230 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="G3" s="11" t="n">
         <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH("ALG-PS-01",'Scope &amp; Sequence'!$I$3:$I$7)))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>249</v>
+        <v>213</v>
       </c>
       <c r="G4" s="11" t="n">
         <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH("ALG-IM-03",'Scope &amp; Sequence'!$I$3:$I$7)))</f>
         <v>1</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>249</v>
+        <v>213</v>
       </c>
       <c r="G5" s="11" t="n">
         <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH("SYS-SE-13",'Scope &amp; Sequence'!$I$3:$I$7)))</f>
         <v>1</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G6" s="11" t="n">
         <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH("PRO-PD",'Scope &amp; Sequence'!$I$3:$I$7)))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D7" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="F7" s="11" t="s">
         <v>264</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>244</v>
       </c>
       <c r="G7" s="11" t="n">
         <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH("PRO-VD",'Scope &amp; Sequence'!$I$3:$I$7)))</f>
         <v>4</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="G8" s="11" t="n">
         <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH("PRO-RD",'Scope &amp; Sequence'!$I$3:$I$7)))</f>
         <v>3</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="20" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G9" s="11" t="n">
         <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH("PRO-TR",'Scope &amp; Sequence'!$I$3:$I$7)))</f>
         <v>3</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3298,17 +3316,17 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -3320,7 +3338,7 @@
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -3332,7 +3350,7 @@
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -3344,7 +3362,7 @@
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -3377,7 +3395,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -3389,7 +3407,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3397,19 +3415,19 @@
         <v>39</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3417,19 +3435,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3437,19 +3455,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3457,19 +3475,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3477,19 +3495,19 @@
         <v>1</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3497,19 +3515,19 @@
         <v>1</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3517,19 +3535,19 @@
         <v>2</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3537,19 +3555,19 @@
         <v>2</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3557,19 +3575,19 @@
         <v>2</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3577,119 +3595,133 @@
         <v>2</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="n">
-        <v>3</v>
+      <c r="A12" s="11" t="s">
+        <v>139</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="n">
-        <v>3</v>
+      <c r="A13" s="11" t="s">
+        <v>139</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="n">
-        <v>4</v>
+      <c r="A14" s="11" t="s">
+        <v>159</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="n">
-        <v>4</v>
+      <c r="A15" s="11" t="s">
+        <v>159</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="n">
-        <v>5</v>
+      <c r="A16" s="11" t="s">
+        <v>189</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>360</v>
+        <v>363</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -3719,124 +3751,124 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -3845,7 +3877,7 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -3854,7 +3886,7 @@
     </row>
     <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -3863,7 +3895,7 @@
     </row>
     <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -3872,7 +3904,7 @@
     </row>
     <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>

--- a/ThemePark_Engineers_Grade5_Python_Camp_MASTER.xlsx
+++ b/ThemePark_Engineers_Grade5_Python_Camp_MASTER.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="406">
   <si>
     <t xml:space="preserve">Theme Park Engineers - Grade 5 Python Camp</t>
   </si>
@@ -186,10 +186,10 @@
     <t xml:space="preserve">How do I make a computer do exactly what I say - and repeat it without repeating myself?</t>
   </si>
   <si>
-    <t xml:space="preserve">Run a Python program and read its output; identify a syntax error from a traceback and correct it; assign and reassign variables with meaningful names; retrieve typed input and convert it with int(); build an f-string receipt; use a for loop with range() to repeat drawing steps; calculate any polygon's turn angle as 360/sides.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">print(), strings, comments (#), variables, input(), int(), f-strings, turtle, for, range()</t>
+    <t xml:space="preserve">Run a Python program and read its output; identify a syntax error from a traceback and correct it; assign and reassign variables with meaningful names; retrieve typed input and convert it with int(); build an f-string receipt; use a for loop with range() to repeat drawing steps; calculate any polygon's turn angle as 360/sides. Name a block of code with def and call it by its name.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">print(), strings, comments (#), variables, input(), int(), f-strings, turtle, for, range(), def + calling it (no parameters)</t>
   </si>
   <si>
     <t xml:space="preserve">Park marquee + Ticket Booth greeter + polygon coaster track drawn with a loop</t>
@@ -198,10 +198,10 @@
     <t xml:space="preserve">PRO-PD; PRO-TR; PRO-VD; ALG-PS-01</t>
   </si>
   <si>
-    <t xml:space="preserve">Cold-call: predict the output before running. Trace table for the ticket-price program. Class track-geometry chart (360/sides).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Believing the computer infers intent. Reading = as 'equals' rather than 'gets'. Believing the loop body runs once. Using the interior angle instead of 360/sides.</t>
+    <t xml:space="preserve">Cold-call: predict the output before running. Trace table for the ticket-price program. Class track-geometry chart (360/sides). Run the defined-but-never-called marquee and sit with the silence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Believing the computer infers intent. Reading = as 'equals' rather than 'gets'. Believing the loop body runs once. Using the interior angle instead of 360/sides. Defining is calling - the silent marquee is the first diagnosis.</t>
   </si>
   <si>
     <t xml:space="preserve">Safety Gates &amp; the Midway - Selection, Lists &amp; the Toolbox</t>
@@ -213,7 +213,7 @@
     <t xml:space="preserve">How does a program decide, remember, surprise - and stamp?</t>
   </si>
   <si>
-    <t xml:space="preserve">Write conditions using comparison operators; branch with if / elif / else; explain why only one branch executes; create a list and pick items out by index; select a random element with random.choice(); define a function with def, call it by name, and pass a parameter to change its behavior</t>
+    <t xml:space="preserve">Write conditions using comparison operators; branch with if / elif / else; explain why only one branch executes; create a list and pick items out by index; select a random element with random.choice(); refactor copied code into a single function and pass a parameter to change its behavior (deepening Monday's def)</t>
   </si>
   <si>
     <t xml:space="preserve">if / elif / else, ==, &lt;, &gt;, booleans, lists, indexing, len(), random.choice(), def, parameters</t>
@@ -240,7 +240,7 @@
     <t xml:space="preserve">Can I plan, build, and soft-launch a ride of my own - and where does a roller coaster's speed come from?</t>
   </si>
   <si>
-    <t xml:space="preserve">Trace a live simulation against a track list using the on-screen dashboard; design a coaster track that completes (first hill tallest, ends at 0) and revise it with a goal; build an Operator's Booth with sequence, a loop, and a decision that selects the track; narrate the three physics lines at a one-partner soft launch; read a traceback and debug independently during the build.</t>
+    <t xml:space="preserve">Trace a live simulation against a track list using the on-screen dashboard; design a coaster track that completes (first hill tallest, ends at 0) and revise it with a goal; build an Operator's Booth with sequence, a loop, and a decision that selects the track; narrate the three physics lines at a one-partner soft launch; read a traceback and debug independently during the build. Organize the booth's welcome and ride list into a named show_menu() function.</t>
   </si>
   <si>
     <t xml:space="preserve">None new - the pygame coaster engine is provided read-only (math.sqrt, the track list, and the position line all previewed on Day 2); student-selected review</t>
@@ -267,10 +267,10 @@
     <t xml:space="preserve">Can I repair my own build - and make it better than it was?</t>
   </si>
   <si>
-    <t xml:space="preserve">Independently diagnose and fix errors in their own program by reading the error first; ship one tested upgrade with a what-changed-and-why note; verify their own track against the live dashboard on Ride Log Grid B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None new - repair and refinement; stretch: a friction term in the drop line, a random.choice mystery track</t>
+    <t xml:space="preserve">Independently diagnose and fix errors in their own program by reading the error first; ship one tested upgrade with a what-changed-and-why note; verify their own track against the live dashboard on Ride Log Grid B Refactor a working program into named functions without changing its behavior (the Tidy Booth).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None new - repair and refinement; stretch: a friction term in the drop line, a random.choice mystery track, the Tidy Booth refactor</t>
   </si>
   <si>
     <t xml:space="preserve">The repaired ride + one shipped upgrade (Version 3) + completed Ride Log Grid B</t>
@@ -396,13 +396,13 @@
     <t xml:space="preserve">Build Block B</t>
   </si>
   <si>
-    <t xml:space="preserve">input(), int(), f-strings - then the turtle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Ticket Booth: greet the guest, ask tickets, hit the '2' + '3' bug, convert at the door with int(), print the f-string receipt. Then the drafting turtle: draw the square track the long way (eight lines), count the copies, rewrite with for and range(), and unlock any polygon with 360 / sides.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trace table for the ticket program. What angle for an octagon track?</t>
+    <t xml:space="preserve">input(), int(), f-strings - then the turtle + def</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Ticket Booth: greet the guest, ask tickets, hit the '2' + '3' bug, convert at the door with int(), print the f-string receipt. Then the drafting turtle: draw the square track the long way (eight lines), count the copies, rewrite with for and range(), and unlock any polygon with 360 / sides. Close with def: the marquee wrapped in show_marquee(), called twice - run the silent no-call version first and name what happened.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trace table for the ticket program. What angle for an octagon track? What are the two steps to using a stamp?</t>
   </si>
   <si>
     <t xml:space="preserve">Ticket-price sign; turtle command reference; sides/angle chart poster</t>
@@ -546,7 +546,7 @@
     <t xml:space="preserve">Capstone blueprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Design the Operator's Booth: a visual blueprint with sequence, one loop, one decision that chooses the track, and named variables. Approval gate: a new track list alone is not a capstone.</t>
+    <t xml:space="preserve">Design the Operator's Booth: a visual blueprint with sequence, one loop, one decision that chooses the track, and named variables. Approval gate: a new track list alone is not a capstone. Every blueprint box gets a stamp-name; the booth's welcome and menu ship as def show_menu().</t>
   </si>
   <si>
     <t xml:space="preserve">Blueprint approved and signed.</t>
@@ -627,7 +627,7 @@
     <t xml:space="preserve">Stretch Garage</t>
   </si>
   <si>
-    <t xml:space="preserve">Every camper picks one upgrade: friction in the drop line (tune 0.01 toward 0.08 to make a 99 m build land on Fury 325s real 95 mph), the random.choice mystery track, a second booth decision, or a track redesign with a goal (Version 3). Working version into a comment first.</t>
+    <t xml:space="preserve">Every camper picks one upgrade: friction in the drop line (tune 0.01 toward 0.08 to make a 99 m build land on Fury 325s real 95 mph), the random.choice mystery track, a second booth decision, the Tidy Booth refactor (repeated lines into a named function - behavior unchanged is the proof), or a track redesign with a goal (Version 3). Working version into a comment first.</t>
   </si>
   <si>
     <t xml:space="preserve">Upgrade chosen and started; working copy protected in a comment.</t>
@@ -822,7 +822,7 @@
     <t xml:space="preserve">1, 2, 3, 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Working park artifact each day; Day-2 refactor of the copied supports into draw_wheel; the Day-4 upgrade note (what changed and why).</t>
+    <t xml:space="preserve">Working park artifact each day, plus the functional-thinking thread: named marquee (Day 1), parameter stamp and the supports refactor (Day 2), named booth blocks with show_menu() (Day 3), the behavior-preserving Tidy Booth refactor and its upgrade note (Day 4). return is deliberately excluded at grade 5 - functions are named blocks.</t>
   </si>
   <si>
     <t xml:space="preserve">E5-PRO-VD-??</t>
@@ -1044,10 +1044,13 @@
     <t xml:space="preserve">The list is the shelf; the index picks the ride.</t>
   </si>
   <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Defining is calling</t>
   </si>
   <si>
-    <t xml:space="preserve">draw_wheel() defined, program runs, nothing draws, camper assumes it broke.</t>
+    <t xml:space="preserve">show_marquee() defined, program runs, nothing prints, camper assumes it broke.</t>
   </si>
   <si>
     <t xml:space="preserve">Writing the code feels like the work is done.</t>
@@ -3612,22 +3615,22 @@
     </row>
     <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>139</v>
+        <v>339</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3635,19 +3638,19 @@
         <v>139</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3655,19 +3658,19 @@
         <v>159</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3675,19 +3678,19 @@
         <v>159</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3695,33 +3698,33 @@
         <v>189</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>213</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -3751,124 +3754,124 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -3877,7 +3880,7 @@
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -3886,7 +3889,7 @@
     </row>
     <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -3895,7 +3898,7 @@
     </row>
     <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -3904,7 +3907,7 @@
     </row>
     <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>

--- a/ThemePark_Engineers_Grade5_Python_Camp_MASTER.xlsx
+++ b/ThemePark_Engineers_Grade5_Python_Camp_MASTER.xlsx
@@ -270,7 +270,7 @@
     <t xml:space="preserve">Independently diagnose and fix errors in their own program by reading the error first; ship one tested upgrade with a what-changed-and-why note; verify their own track against the live dashboard on Ride Log Grid B Refactor a working program into named functions without changing its behavior (the Tidy Booth).</t>
   </si>
   <si>
-    <t xml:space="preserve">None new - repair and refinement; stretch: a friction term in the drop line, a random.choice mystery track, the Tidy Booth refactor</t>
+    <t xml:space="preserve">None new - repair and refinement; stretch: a friction term in the drop line, a random.choice mystery track, the Tidy Booth refactor, the Loop Garage loop-de-loop (extension page)</t>
   </si>
   <si>
     <t xml:space="preserve">The repaired ride + one shipped upgrade (Version 3) + completed Ride Log Grid B</t>
